--- a/results/canaliculi/543_z13c1-2/measurements.xlsx
+++ b/results/canaliculi/543_z13c1-2/measurements.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105.1333</v>
+        <v>144.5455</v>
       </c>
       <c r="C6" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="D6" t="n">
-        <v>62.3789</v>
+        <v>53.1514</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132.068</v>
+        <v>153.1492</v>
       </c>
       <c r="C7" t="n">
-        <v>122.7247</v>
+        <v>133.0692</v>
       </c>
       <c r="D7" t="n">
-        <v>52.7391</v>
+        <v>48.1055</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,13 +739,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>12571.9981</v>
+        <v>23302.6468</v>
       </c>
       <c r="D9" t="n">
-        <v>142.8636</v>
+        <v>172.6122</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +761,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>3526.2724</v>
+        <v>12211.3017</v>
       </c>
       <c r="D10" t="n">
-        <v>113.7507</v>
+        <v>118.5563</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +783,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>3429.3902</v>
+        <v>10973.1197</v>
       </c>
       <c r="D11" t="n">
-        <v>95.2608</v>
+        <v>105.5108</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,106 +805,18 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="C12" t="n">
-        <v>6421.3418</v>
+        <v>51800.8091</v>
       </c>
       <c r="D12" t="n">
-        <v>89.1853</v>
+        <v>252.6869</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>43</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2749.0277</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63.9309</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>63</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5819.5335</v>
-      </c>
-      <c r="D14" t="n">
-        <v>92.37350000000001</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>64</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5684.1458</v>
-      </c>
-      <c r="D15" t="n">
-        <v>88.81480000000001</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>137</v>
-      </c>
-      <c r="C16" t="n">
-        <v>35560.4044</v>
-      </c>
-      <c r="D16" t="n">
-        <v>259.565</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>px</t>
         </is>

--- a/results/canaliculi/543_z13c1-2/measurements.xlsx
+++ b/results/canaliculi/543_z13c1-2/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144.5455</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>53.1514</v>
+        <v>44.8464</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.1492</v>
+        <v>128.0738</v>
       </c>
       <c r="C7" t="n">
-        <v>133.0692</v>
+        <v>121.862</v>
       </c>
       <c r="D7" t="n">
-        <v>48.1055</v>
+        <v>77.041</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>251</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>57581.2348</v>
+        <v>38857.9564</v>
       </c>
       <c r="D2" t="n">
-        <v>229.4073</v>
+        <v>260.7917</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>18363.5447</v>
+        <v>22112.9004</v>
       </c>
       <c r="D3" t="n">
-        <v>133.0692</v>
+        <v>197.4366</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>204</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>32931.4275</v>
+        <v>5483.7884</v>
       </c>
       <c r="D4" t="n">
-        <v>161.4286</v>
+        <v>121.862</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>8488.7034</v>
+        <v>1573.7981</v>
       </c>
       <c r="D5" t="n">
-        <v>113.1827</v>
+        <v>58.2888</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>16520.7306</v>
+        <v>8660.9359</v>
       </c>
       <c r="D6" t="n">
-        <v>144.9187</v>
+        <v>131.2263</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>16690.5658</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>122.7247</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>16318.0321</v>
+        <v>17440.3639</v>
       </c>
       <c r="D8" t="n">
-        <v>130.5443</v>
+        <v>166.0987</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>23302.6468</v>
+        <v>5594.2564</v>
       </c>
       <c r="D9" t="n">
-        <v>172.6122</v>
+        <v>99.8974</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>12211.3017</v>
+        <v>3383.3557</v>
       </c>
       <c r="D10" t="n">
-        <v>118.5563</v>
+        <v>78.6827</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>10973.1197</v>
+        <v>3262.915</v>
       </c>
       <c r="D11" t="n">
-        <v>105.5108</v>
+        <v>75.8817</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="C12" t="n">
-        <v>51800.8091</v>
+        <v>24706.9597</v>
       </c>
       <c r="D12" t="n">
-        <v>252.6869</v>
+        <v>218.6457</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>

--- a/results/canaliculi/543_z13c1-2/measurements.xlsx
+++ b/results/canaliculi/543_z13c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>69</v>
-      </c>
-      <c r="C6" t="n">
-        <v>56</v>
-      </c>
-      <c r="D6" t="n">
-        <v>44.8464</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>11</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>34.5455</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.7682</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>971.1769</v>
+      </c>
+      <c r="C8" t="n">
+        <v>544.2742</v>
+      </c>
+      <c r="D8" t="n">
+        <v>811.5424</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>128.0738</v>
-      </c>
-      <c r="C7" t="n">
-        <v>121.862</v>
-      </c>
-      <c r="D7" t="n">
-        <v>77.041</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>27.8598</v>
+      </c>
+      <c r="C9" t="n">
+        <v>27.6638</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.1134</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>38857.9564</v>
+        <v>2735.6206</v>
       </c>
       <c r="D2" t="n">
-        <v>260.7917</v>
+        <v>28.796</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>22112.9004</v>
+        <v>1373.9037</v>
       </c>
       <c r="D3" t="n">
-        <v>197.4366</v>
+        <v>32.712</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>5483.7884</v>
+        <v>544.2742</v>
       </c>
       <c r="D4" t="n">
-        <v>121.862</v>
+        <v>24.7397</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>1573.7981</v>
+        <v>525.5879</v>
       </c>
       <c r="D5" t="n">
-        <v>58.2888</v>
+        <v>32.8492</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>8660.9359</v>
+        <v>961.5067</v>
       </c>
       <c r="D6" t="n">
-        <v>131.2263</v>
+        <v>24.654</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>267.9655</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>17.8644</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>17440.3639</v>
+        <v>167.7523</v>
       </c>
       <c r="D8" t="n">
-        <v>166.0987</v>
+        <v>20.969</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>5594.2564</v>
+        <v>1510.0773</v>
       </c>
       <c r="D9" t="n">
-        <v>99.8974</v>
+        <v>29.0399</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>3383.3557</v>
+        <v>345.6346</v>
       </c>
       <c r="D10" t="n">
-        <v>78.6827</v>
+        <v>23.0423</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>3262.915</v>
+        <v>397.1493</v>
       </c>
       <c r="D11" t="n">
-        <v>75.8817</v>
+        <v>44.1277</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>24706.9597</v>
+        <v>1853.4743</v>
       </c>
       <c r="D12" t="n">
-        <v>218.6457</v>
+        <v>27.6638</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>

--- a/results/canaliculi/543_z13c1-2/measurements.xlsx
+++ b/results/canaliculi/543_z13c1-2/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.5455</v>
+        <v>63.5455</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>27.7682</v>
+        <v>56.0185</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>971.1769</v>
+        <v>1713.9866</v>
       </c>
       <c r="C8" t="n">
-        <v>544.2742</v>
+        <v>1167.8742</v>
       </c>
       <c r="D8" t="n">
-        <v>811.5424</v>
+        <v>1503.6864</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.8598</v>
+        <v>26.8926</v>
       </c>
       <c r="C9" t="n">
-        <v>27.6638</v>
+        <v>27.1599</v>
       </c>
       <c r="D9" t="n">
-        <v>7.1134</v>
+        <v>4.8368</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1028094</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>45033</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04380241</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>643</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00062543</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.07e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>659</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>68.33540000000001</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -646,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>2735.6206</v>
+        <v>4094.9457</v>
       </c>
       <c r="D2" t="n">
-        <v>28.796</v>
+        <v>26.7644</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -668,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>1373.9037</v>
+        <v>1843.9941</v>
       </c>
       <c r="D3" t="n">
-        <v>32.712</v>
+        <v>28.3691</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -690,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>544.2742</v>
+        <v>915.0092</v>
       </c>
       <c r="D4" t="n">
-        <v>24.7397</v>
+        <v>27.7276</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>525.5879</v>
+        <v>515.6884</v>
       </c>
       <c r="D5" t="n">
-        <v>32.8492</v>
+        <v>36.8349</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="C6" t="n">
-        <v>961.5067</v>
+        <v>4189.1934</v>
       </c>
       <c r="D6" t="n">
-        <v>24.654</v>
+        <v>27.928</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>267.9655</v>
+        <v>284.9361</v>
       </c>
       <c r="D7" t="n">
-        <v>17.8644</v>
+        <v>17.8085</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -781,10 +982,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>167.7523</v>
+        <v>167.5807</v>
       </c>
       <c r="D8" t="n">
-        <v>20.969</v>
+        <v>20.9476</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>1510.0773</v>
+        <v>1859.2977</v>
       </c>
       <c r="D9" t="n">
-        <v>29.0399</v>
+        <v>26.9463</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>345.6346</v>
+        <v>1167.8742</v>
       </c>
       <c r="D10" t="n">
-        <v>23.0423</v>
+        <v>27.1599</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -844,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>397.1493</v>
+        <v>511.9605</v>
       </c>
       <c r="D11" t="n">
-        <v>44.1277</v>
+        <v>30.1153</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -866,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="C12" t="n">
-        <v>1853.4743</v>
+        <v>3303.3729</v>
       </c>
       <c r="D12" t="n">
-        <v>27.6638</v>
+        <v>25.2166</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
